--- a/resources/modele_flux.xlsx
+++ b/resources/modele_flux.xlsx
@@ -779,8 +779,9 @@
           <t>Flux de trésorerie provenant des capitaux propres (somme FK à FN)</t>
         </is>
       </c>
-      <c r="B42" t="e">
-        <v>#NAME?</v>
+      <c r="B42">
+        <f>-CtaCptSolde("10*")+CtaCptSoldeNm1("10*")-CtaCptSolde("14*")+CtaCptSoldeNm1("14*")</f>
+        <v/>
       </c>
     </row>
     <row r="43">
@@ -814,8 +815,9 @@
           <t>Flux de trésorerie provenant des capitaux étrangers (somme FO à FQ)</t>
         </is>
       </c>
-      <c r="B46" t="e">
-        <v>#NAME?</v>
+      <c r="B46">
+        <f>-CtaCptSolde("16*")+CtaCptSoldeNm1("16*")</f>
+        <v/>
       </c>
     </row>
     <row r="47">
